--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0080.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0080.xlsx
@@ -27132,7 +27132,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Vậy là cậu có thể vào Dark Tide. Khó怪 là chúng ta không tìm thấy cậu.</t>
+          <t>Vậy là cậu có thể vào Dark Tide. Thảo nào chúng ta không tìm thấy cậu.</t>
         </is>
       </c>
     </row>
